--- a/data/winter_data.xlsx
+++ b/data/winter_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB21"/>
+  <dimension ref="A1:AA21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -469,90 +469,85 @@
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>泥水状况</t>
+          <t>DO(mg/L)</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>DO(mg/L)</t>
+          <t>NaCl(mg/L)</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>NaCl(mg/L)</t>
+          <t>电导率(uS/cm)</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
         <is>
-          <t>电导率(uS/cm)</t>
+          <t>液温</t>
         </is>
       </c>
       <c r="O1" t="inlineStr">
         <is>
-          <t>液温</t>
+          <t>pH</t>
         </is>
       </c>
       <c r="P1" t="inlineStr">
         <is>
-          <t>pH</t>
+          <t>H2S</t>
         </is>
       </c>
       <c r="Q1" t="inlineStr">
         <is>
-          <t>H2S</t>
+          <t>TOC（mg/L)</t>
         </is>
       </c>
       <c r="R1" t="inlineStr">
         <is>
-          <t>TOC（mg/L)</t>
+          <t>TC(mg/L)</t>
         </is>
       </c>
       <c r="S1" t="inlineStr">
         <is>
-          <t>TC(mg/L)</t>
+          <t>IC(mg/L)</t>
         </is>
       </c>
       <c r="T1" t="inlineStr">
         <is>
-          <t>IC(mg/L)</t>
+          <t>总氮（mg/L)</t>
         </is>
       </c>
       <c r="U1" t="inlineStr">
         <is>
-          <t>总氮（mg/L)</t>
+          <t>总磷（mg/L)</t>
         </is>
       </c>
       <c r="V1" t="inlineStr">
         <is>
-          <t>总磷（mg/L)</t>
+          <t>铵态氮（mg/L)</t>
         </is>
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>铵态氮（mg/L)</t>
+          <t>硝态氮（mg/L)</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>硝态氮（mg/L)</t>
+          <t>COD（mg/L)</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
         <is>
-          <t>COD（mg/L)</t>
+          <t>采样时间</t>
         </is>
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>采样时间</t>
+          <t>采样时段</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
-        <is>
-          <t>采样时段</t>
-        </is>
-      </c>
-      <c r="AB1" t="inlineStr">
         <is>
           <t>季节</t>
         </is>
@@ -591,11 +586,7 @@
       <c r="J2" t="n">
         <v>14</v>
       </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>无水无泥</t>
-        </is>
-      </c>
+      <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
@@ -609,16 +600,15 @@
       <c r="V2" t="inlineStr"/>
       <c r="W2" t="inlineStr"/>
       <c r="X2" t="inlineStr"/>
-      <c r="Y2" t="inlineStr"/>
-      <c r="Z2" t="n">
+      <c r="Y2" t="n">
         <v>1.16</v>
       </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>10:00:00</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
-        <is>
-          <t>10:00:00</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
         <is>
           <t>冬季</t>
         </is>
@@ -657,60 +647,55 @@
       <c r="J3" t="n">
         <v>13</v>
       </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>有水泥少</t>
-        </is>
+      <c r="K3" t="n">
+        <v>5.42</v>
       </c>
       <c r="L3" t="n">
-        <v>5.42</v>
+        <v>739</v>
       </c>
       <c r="M3" t="n">
-        <v>739</v>
+        <v>1156</v>
       </c>
       <c r="N3" t="n">
-        <v>1156</v>
+        <v>10.3</v>
       </c>
       <c r="O3" t="n">
-        <v>10.3</v>
-      </c>
-      <c r="P3" t="n">
         <v>7.16</v>
       </c>
-      <c r="Q3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="n">
+        <v>54.08</v>
+      </c>
       <c r="R3" t="n">
-        <v>54.08</v>
+        <v>183.4</v>
       </c>
       <c r="S3" t="n">
-        <v>183.4</v>
+        <v>129.3</v>
       </c>
       <c r="T3" t="n">
-        <v>129.3</v>
+        <v>122.55</v>
       </c>
       <c r="U3" t="n">
-        <v>122.55</v>
+        <v>8.4</v>
       </c>
       <c r="V3" t="n">
-        <v>8.4</v>
+        <v>114.05</v>
       </c>
       <c r="W3" t="n">
-        <v>114.05</v>
+        <v>0.95</v>
       </c>
       <c r="X3" t="n">
-        <v>0.95</v>
+        <v>1713.08</v>
       </c>
       <c r="Y3" t="n">
-        <v>1713.08</v>
-      </c>
-      <c r="Z3" t="n">
         <v>1.16</v>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>10:25:00</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
-        <is>
-          <t>10:25:00</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
         <is>
           <t>冬季</t>
         </is>
@@ -749,60 +734,55 @@
       <c r="J4" t="n">
         <v>14</v>
       </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>有水无泥</t>
-        </is>
+      <c r="K4" t="n">
+        <v>6.93</v>
       </c>
       <c r="L4" t="n">
-        <v>6.93</v>
+        <v>365</v>
       </c>
       <c r="M4" t="n">
-        <v>365</v>
+        <v>625</v>
       </c>
       <c r="N4" t="n">
-        <v>625</v>
+        <v>16.7</v>
       </c>
       <c r="O4" t="n">
-        <v>16.7</v>
-      </c>
-      <c r="P4" t="n">
         <v>7.28</v>
       </c>
-      <c r="Q4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="n">
+        <v>21.42</v>
+      </c>
       <c r="R4" t="n">
-        <v>21.42</v>
+        <v>106.6</v>
       </c>
       <c r="S4" t="n">
-        <v>106.6</v>
+        <v>85.16</v>
       </c>
       <c r="T4" t="n">
-        <v>85.16</v>
+        <v>54.73</v>
       </c>
       <c r="U4" t="n">
-        <v>54.73</v>
+        <v>1.18</v>
       </c>
       <c r="V4" t="n">
-        <v>1.18</v>
+        <v>27.76</v>
       </c>
       <c r="W4" t="n">
-        <v>27.76</v>
+        <v>2.04</v>
       </c>
       <c r="X4" t="n">
-        <v>2.04</v>
+        <v>574.91</v>
       </c>
       <c r="Y4" t="n">
-        <v>574.91</v>
-      </c>
-      <c r="Z4" t="n">
         <v>1.15</v>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>16:37:00</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
-        <is>
-          <t>16:37:00</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
         <is>
           <t>冬季</t>
         </is>
@@ -841,11 +821,7 @@
       <c r="J5" t="n">
         <v>14</v>
       </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>无水无泥</t>
-        </is>
-      </c>
+      <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
@@ -859,16 +835,15 @@
       <c r="V5" t="inlineStr"/>
       <c r="W5" t="inlineStr"/>
       <c r="X5" t="inlineStr"/>
-      <c r="Y5" t="inlineStr"/>
-      <c r="Z5" t="n">
+      <c r="Y5" t="n">
         <v>1.15</v>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>16:22:00</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
-        <is>
-          <t>16:22:00</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
         <is>
           <t>冬季</t>
         </is>
@@ -907,11 +882,7 @@
       <c r="J6" t="n">
         <v>14</v>
       </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>无水无泥</t>
-        </is>
-      </c>
+      <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
@@ -925,16 +896,15 @@
       <c r="V6" t="inlineStr"/>
       <c r="W6" t="inlineStr"/>
       <c r="X6" t="inlineStr"/>
-      <c r="Y6" t="inlineStr"/>
-      <c r="Z6" t="n">
+      <c r="Y6" t="n">
         <v>1.15</v>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>16:06:00</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
-        <is>
-          <t>16:06:00</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
         <is>
           <t>冬季</t>
         </is>
@@ -973,11 +943,7 @@
       <c r="J7" t="n">
         <v>14</v>
       </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>无水无泥</t>
-        </is>
-      </c>
+      <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
@@ -991,16 +957,15 @@
       <c r="V7" t="inlineStr"/>
       <c r="W7" t="inlineStr"/>
       <c r="X7" t="inlineStr"/>
-      <c r="Y7" t="inlineStr"/>
-      <c r="Z7" t="n">
+      <c r="Y7" t="n">
         <v>1.15</v>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>15:53:00</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
-        <is>
-          <t>15:53:00</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
         <is>
           <t>冬季</t>
         </is>
@@ -1039,62 +1004,57 @@
       <c r="J8" t="n">
         <v>13</v>
       </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>有水无泥</t>
-        </is>
-      </c>
-      <c r="L8" t="n">
+      <c r="K8" t="n">
         <v>7.03</v>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>16.48g/L</t>
         </is>
       </c>
+      <c r="M8" t="n">
+        <v>21.65</v>
+      </c>
       <c r="N8" t="n">
-        <v>21.65</v>
+        <v>13.5</v>
       </c>
       <c r="O8" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="P8" t="n">
         <v>7.44</v>
       </c>
-      <c r="Q8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="n">
+        <v>8.978999999999999</v>
+      </c>
       <c r="R8" t="n">
-        <v>8.978999999999999</v>
+        <v>43.46</v>
       </c>
       <c r="S8" t="n">
-        <v>43.46</v>
+        <v>34.48</v>
       </c>
       <c r="T8" t="n">
-        <v>34.48</v>
+        <v>20.42</v>
       </c>
       <c r="U8" t="n">
-        <v>20.42</v>
+        <v>0.23</v>
       </c>
       <c r="V8" t="n">
-        <v>0.23</v>
+        <v>6</v>
       </c>
       <c r="W8" t="n">
-        <v>6</v>
+        <v>1.02</v>
       </c>
       <c r="X8" t="n">
-        <v>1.02</v>
+        <v>12139.18</v>
       </c>
       <c r="Y8" t="n">
-        <v>12139.18</v>
-      </c>
-      <c r="Z8" t="n">
         <v>1.16</v>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>14:56:00</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
-        <is>
-          <t>14:56:00</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
         <is>
           <t>冬季</t>
         </is>
@@ -1133,19 +1093,15 @@
       <c r="J9" t="n">
         <v>13</v>
       </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>无水无泥</t>
-        </is>
-      </c>
+      <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
-      <c r="P9" t="inlineStr"/>
-      <c r="Q9" t="n">
+      <c r="P9" t="n">
         <v>1.2</v>
       </c>
+      <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr"/>
       <c r="S9" t="inlineStr"/>
       <c r="T9" t="inlineStr"/>
@@ -1153,16 +1109,15 @@
       <c r="V9" t="inlineStr"/>
       <c r="W9" t="inlineStr"/>
       <c r="X9" t="inlineStr"/>
-      <c r="Y9" t="inlineStr"/>
-      <c r="Z9" t="n">
+      <c r="Y9" t="n">
         <v>1.16</v>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>15:34:00</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
-        <is>
-          <t>15:34:00</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
         <is>
           <t>冬季</t>
         </is>
@@ -1201,62 +1156,57 @@
       <c r="J10" t="n">
         <v>13</v>
       </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>有水无泥</t>
-        </is>
+      <c r="K10" t="n">
+        <v>10.45</v>
       </c>
       <c r="L10" t="n">
-        <v>10.45</v>
+        <v>437</v>
       </c>
       <c r="M10" t="n">
-        <v>437</v>
+        <v>695</v>
       </c>
       <c r="N10" t="n">
-        <v>695</v>
+        <v>14.3</v>
       </c>
       <c r="O10" t="n">
-        <v>14.3</v>
+        <v>7.94</v>
       </c>
       <c r="P10" t="n">
-        <v>7.94</v>
+        <v>1.4</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.4</v>
+        <v>17.11</v>
       </c>
       <c r="R10" t="n">
-        <v>17.11</v>
+        <v>81.48999999999999</v>
       </c>
       <c r="S10" t="n">
-        <v>81.48999999999999</v>
+        <v>64.37</v>
       </c>
       <c r="T10" t="n">
-        <v>64.37</v>
+        <v>33.3</v>
       </c>
       <c r="U10" t="n">
-        <v>33.3</v>
+        <v>7.11</v>
       </c>
       <c r="V10" t="n">
-        <v>7.11</v>
+        <v>21.59</v>
       </c>
       <c r="W10" t="n">
-        <v>21.59</v>
+        <v>2.98</v>
       </c>
       <c r="X10" t="n">
-        <v>2.98</v>
+        <v>687.5599999999999</v>
       </c>
       <c r="Y10" t="n">
-        <v>687.5599999999999</v>
-      </c>
-      <c r="Z10" t="n">
         <v>1.16</v>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>15:45:00</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
-        <is>
-          <t>15:45:00</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
         <is>
           <t>冬季</t>
         </is>
@@ -1295,11 +1245,7 @@
       <c r="J11" t="n">
         <v>1</v>
       </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>无水无泥</t>
-        </is>
-      </c>
+      <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
@@ -1313,16 +1259,15 @@
       <c r="V11" t="inlineStr"/>
       <c r="W11" t="inlineStr"/>
       <c r="X11" t="inlineStr"/>
-      <c r="Y11" t="inlineStr"/>
-      <c r="Z11" t="n">
+      <c r="Y11" t="n">
         <v>1.19</v>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>10:30:00</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
-        <is>
-          <t>10:30:00</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
         <is>
           <t>冬季</t>
         </is>
@@ -1361,11 +1306,7 @@
       <c r="J12" t="n">
         <v>1</v>
       </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>无水无泥</t>
-        </is>
-      </c>
+      <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
@@ -1379,16 +1320,15 @@
       <c r="V12" t="inlineStr"/>
       <c r="W12" t="inlineStr"/>
       <c r="X12" t="inlineStr"/>
-      <c r="Y12" t="inlineStr"/>
-      <c r="Z12" t="n">
+      <c r="Y12" t="n">
         <v>1.19</v>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>10:45:00</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
-        <is>
-          <t>10:45:00</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
         <is>
           <t>冬季</t>
         </is>
@@ -1427,11 +1367,7 @@
       <c r="J13" t="n">
         <v>1</v>
       </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>无水无泥</t>
-        </is>
-      </c>
+      <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
@@ -1445,16 +1381,15 @@
       <c r="V13" t="inlineStr"/>
       <c r="W13" t="inlineStr"/>
       <c r="X13" t="inlineStr"/>
-      <c r="Y13" t="inlineStr"/>
-      <c r="Z13" t="n">
+      <c r="Y13" t="n">
         <v>1.19</v>
       </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>10:55:00</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
-        <is>
-          <t>10:55:00</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
         <is>
           <t>冬季</t>
         </is>
@@ -1495,60 +1430,55 @@
       <c r="J14" t="n">
         <v>1</v>
       </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>有水无泥</t>
-        </is>
+      <c r="K14" t="n">
+        <v>2.97</v>
       </c>
       <c r="L14" t="n">
-        <v>2.97</v>
+        <v>873</v>
       </c>
       <c r="M14" t="n">
-        <v>873</v>
+        <v>1279</v>
       </c>
       <c r="N14" t="n">
-        <v>1279</v>
+        <v>10.9</v>
       </c>
       <c r="O14" t="n">
-        <v>10.9</v>
-      </c>
-      <c r="P14" t="n">
         <v>7.63</v>
       </c>
-      <c r="Q14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="n">
+        <v>35.03</v>
+      </c>
       <c r="R14" t="n">
-        <v>35.03</v>
+        <v>151.1</v>
       </c>
       <c r="S14" t="n">
-        <v>151.1</v>
+        <v>116</v>
       </c>
       <c r="T14" t="n">
-        <v>116</v>
+        <v>75.04000000000001</v>
       </c>
       <c r="U14" t="n">
-        <v>75.04000000000001</v>
+        <v>5.31</v>
       </c>
       <c r="V14" t="n">
-        <v>5.31</v>
+        <v>70.2</v>
       </c>
       <c r="W14" t="n">
-        <v>70.2</v>
+        <v>0.2</v>
       </c>
       <c r="X14" t="n">
-        <v>0.2</v>
+        <v>590.45</v>
       </c>
       <c r="Y14" t="n">
-        <v>590.45</v>
-      </c>
-      <c r="Z14" t="n">
         <v>1.19</v>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>11:10:00</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
-        <is>
-          <t>11:10:00</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
         <is>
           <t>冬季</t>
         </is>
@@ -1587,60 +1517,55 @@
       <c r="J15" t="n">
         <v>1</v>
       </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>有水无泥</t>
-        </is>
+      <c r="K15" t="n">
+        <v>4.71</v>
       </c>
       <c r="L15" t="n">
-        <v>4.71</v>
+        <v>483</v>
       </c>
       <c r="M15" t="n">
-        <v>483</v>
+        <v>810</v>
       </c>
       <c r="N15" t="n">
-        <v>810</v>
+        <v>18.9</v>
       </c>
       <c r="O15" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="P15" t="n">
         <v>9.25</v>
       </c>
-      <c r="Q15" t="inlineStr"/>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="n">
+        <v>124</v>
+      </c>
       <c r="R15" t="n">
-        <v>124</v>
+        <v>189</v>
       </c>
       <c r="S15" t="n">
-        <v>189</v>
+        <v>64.91</v>
       </c>
       <c r="T15" t="n">
-        <v>64.91</v>
+        <v>5.343</v>
       </c>
       <c r="U15" t="n">
-        <v>5.343</v>
+        <v>0.65</v>
       </c>
       <c r="V15" t="n">
-        <v>0.65</v>
+        <v>0.58</v>
       </c>
       <c r="W15" t="n">
-        <v>0.58</v>
+        <v>2.87</v>
       </c>
       <c r="X15" t="n">
-        <v>2.87</v>
+        <v>1561.58</v>
       </c>
       <c r="Y15" t="n">
-        <v>1561.58</v>
-      </c>
-      <c r="Z15" t="n">
         <v>1.19</v>
       </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>15:02:00</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
-        <is>
-          <t>15:02:00</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
         <is>
           <t>冬季</t>
         </is>
@@ -1679,11 +1604,7 @@
       <c r="J16" t="n">
         <v>1</v>
       </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>无水无泥</t>
-        </is>
-      </c>
+      <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
@@ -1697,16 +1618,15 @@
       <c r="V16" t="inlineStr"/>
       <c r="W16" t="inlineStr"/>
       <c r="X16" t="inlineStr"/>
-      <c r="Y16" t="inlineStr"/>
-      <c r="Z16" t="n">
+      <c r="Y16" t="n">
         <v>1.19</v>
       </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>15:25:00</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
-        <is>
-          <t>15:25:00</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
         <is>
           <t>冬季</t>
         </is>
@@ -1745,60 +1665,55 @@
       <c r="J17" t="n">
         <v>1</v>
       </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>有水无泥</t>
-        </is>
+      <c r="K17" t="n">
+        <v>2.73</v>
       </c>
       <c r="L17" t="n">
-        <v>2.73</v>
+        <v>361</v>
       </c>
       <c r="M17" t="n">
-        <v>361</v>
+        <v>484</v>
       </c>
       <c r="N17" t="n">
-        <v>484</v>
+        <v>8.1</v>
       </c>
       <c r="O17" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="P17" t="n">
         <v>8.76</v>
       </c>
-      <c r="Q17" t="inlineStr"/>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="n">
+        <v>28.43</v>
+      </c>
       <c r="R17" t="n">
-        <v>28.43</v>
+        <v>98.65000000000001</v>
       </c>
       <c r="S17" t="n">
-        <v>98.65000000000001</v>
+        <v>70.23</v>
       </c>
       <c r="T17" t="n">
-        <v>70.23</v>
+        <v>71.54000000000001</v>
       </c>
       <c r="U17" t="n">
-        <v>71.54000000000001</v>
+        <v>5.15</v>
       </c>
       <c r="V17" t="n">
-        <v>5.15</v>
+        <v>55.7</v>
       </c>
       <c r="W17" t="n">
-        <v>55.7</v>
+        <v>0.78</v>
       </c>
       <c r="X17" t="n">
-        <v>0.78</v>
+        <v>940.0599999999999</v>
       </c>
       <c r="Y17" t="n">
-        <v>940.0599999999999</v>
-      </c>
-      <c r="Z17" t="n">
         <v>1.19</v>
       </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>15:35:00</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
-        <is>
-          <t>15:35:00</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
         <is>
           <t>冬季</t>
         </is>
@@ -1837,19 +1752,15 @@
       <c r="J18" t="n">
         <v>1</v>
       </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>无水无泥</t>
-        </is>
-      </c>
+      <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="O18" t="inlineStr"/>
-      <c r="P18" t="inlineStr"/>
-      <c r="Q18" t="n">
+      <c r="P18" t="n">
         <v>5</v>
       </c>
+      <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr"/>
       <c r="S18" t="inlineStr"/>
       <c r="T18" t="inlineStr"/>
@@ -1857,16 +1768,15 @@
       <c r="V18" t="inlineStr"/>
       <c r="W18" t="inlineStr"/>
       <c r="X18" t="inlineStr"/>
-      <c r="Y18" t="inlineStr"/>
-      <c r="Z18" t="n">
+      <c r="Y18" t="n">
         <v>1.19</v>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>16:00:00</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
-        <is>
-          <t>16:00:00</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
         <is>
           <t>冬季</t>
         </is>
@@ -1905,11 +1815,7 @@
       <c r="J19" t="n">
         <v>1</v>
       </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>无水无泥</t>
-        </is>
-      </c>
+      <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
@@ -1923,16 +1829,15 @@
       <c r="V19" t="inlineStr"/>
       <c r="W19" t="inlineStr"/>
       <c r="X19" t="inlineStr"/>
-      <c r="Y19" t="inlineStr"/>
-      <c r="Z19" t="n">
+      <c r="Y19" t="n">
         <v>1.19</v>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>16:27:00</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
-        <is>
-          <t>16:27:00</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
         <is>
           <t>冬季</t>
         </is>
@@ -1971,60 +1876,55 @@
       <c r="J20" t="n">
         <v>1</v>
       </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>有水无泥</t>
-        </is>
+      <c r="K20" t="n">
+        <v>4.15</v>
       </c>
       <c r="L20" t="n">
-        <v>4.15</v>
+        <v>475</v>
       </c>
       <c r="M20" t="n">
-        <v>475</v>
+        <v>731</v>
       </c>
       <c r="N20" t="n">
-        <v>731</v>
+        <v>12.5</v>
       </c>
       <c r="O20" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="P20" t="n">
         <v>9.02</v>
       </c>
-      <c r="Q20" t="inlineStr"/>
+      <c r="P20" t="inlineStr"/>
+      <c r="Q20" t="n">
+        <v>44.99</v>
+      </c>
       <c r="R20" t="n">
-        <v>44.99</v>
+        <v>144</v>
       </c>
       <c r="S20" t="n">
-        <v>144</v>
+        <v>99.03</v>
       </c>
       <c r="T20" t="n">
-        <v>99.03</v>
+        <v>18.97</v>
       </c>
       <c r="U20" t="n">
-        <v>18.97</v>
+        <v>1.35</v>
       </c>
       <c r="V20" t="n">
-        <v>1.35</v>
+        <v>5.22</v>
       </c>
       <c r="W20" t="n">
-        <v>5.22</v>
+        <v>0.08</v>
       </c>
       <c r="X20" t="n">
-        <v>0.08</v>
+        <v>1204.21</v>
       </c>
       <c r="Y20" t="n">
-        <v>1204.21</v>
-      </c>
-      <c r="Z20" t="n">
         <v>1.19</v>
       </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>16:40:00</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
-        <is>
-          <t>16:40:00</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
         <is>
           <t>冬季</t>
         </is>
@@ -2063,11 +1963,7 @@
       <c r="J21" t="n">
         <v>1</v>
       </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>无水无泥</t>
-        </is>
-      </c>
+      <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
@@ -2081,16 +1977,15 @@
       <c r="V21" t="inlineStr"/>
       <c r="W21" t="inlineStr"/>
       <c r="X21" t="inlineStr"/>
-      <c r="Y21" t="inlineStr"/>
-      <c r="Z21" t="n">
+      <c r="Y21" t="n">
         <v>1.19</v>
       </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>16:16:00</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
-        <is>
-          <t>16:16:00</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
         <is>
           <t>冬季</t>
         </is>
